--- a/data/trans_orig/IPAQ_MET-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43224</t>
+          <t>43413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71646</t>
+          <t>73592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>62059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96122</t>
+          <t>95375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200596</t>
+          <t>199480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244079</t>
+          <t>243929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182275</t>
+          <t>184973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220719</t>
+          <t>221087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396803</t>
+          <t>394417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>451856</t>
+          <t>452483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130244</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172750</t>
+          <t>171142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104796</t>
+          <t>104665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>142420</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>247839</t>
+          <t>246912</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>301910</t>
+          <t>303419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,09%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68769</t>
+          <t>69778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96358</t>
+          <t>97565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>193551</t>
+          <t>193953</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>233381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189316</t>
+          <t>190332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>228589</t>
+          <t>227795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392999</t>
+          <t>395068</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448519</t>
+          <t>451090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93941</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129442</t>
+          <t>128800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118620</t>
+          <t>119299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>156908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224183</t>
+          <t>221392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278701</t>
+          <t>274497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80051</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57507</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90641</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231060</t>
+          <t>230034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280963</t>
+          <t>276663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75133</t>
+          <t>75441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101888</t>
+          <t>101237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>314667</t>
+          <t>314156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>368547</t>
+          <t>366892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180054</t>
+          <t>182599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228423</t>
+          <t>227180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81698</t>
+          <t>80891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248606</t>
+          <t>248191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298531</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116218</t>
+          <t>116866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160350</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72310</t>
+          <t>74159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173689</t>
+          <t>172413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225680</t>
+          <t>228809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543827</t>
+          <t>543029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613196</t>
+          <t>614764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361642</t>
+          <t>363125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421362</t>
+          <t>420318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>918843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1015276</t>
+          <t>1016407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>399749</t>
+          <t>400739</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>462529</t>
+          <t>469462</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>347034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>404480</t>
+          <t>405457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>759658</t>
+          <t>762466</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>846209</t>
+          <t>853111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69910</t>
+          <t>69262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102824</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>55851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108506</t>
+          <t>109615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150400</t>
+          <t>151593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>259631</t>
+          <t>262399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>308676</t>
+          <t>311721</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>301970</t>
+          <t>301926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>355807</t>
+          <t>355625</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>573521</t>
+          <t>578103</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>650199</t>
+          <t>653763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226518</t>
+          <t>226122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>277261</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>339043</t>
+          <t>339906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>393132</t>
+          <t>393741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>578905</t>
+          <t>578049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>656244</t>
+          <t>653792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60741</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90829</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53538</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>94685</t>
+          <t>96658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137133</t>
+          <t>137276</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131726</t>
+          <t>130869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166355</t>
+          <t>167482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>447034</t>
+          <t>450612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>513305</t>
+          <t>516655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>594973</t>
+          <t>592451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>667434</t>
+          <t>666013</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>49362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76570</t>
+          <t>77269</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>530104</t>
+          <t>527249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>593765</t>
+          <t>596748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>582609</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>659395</t>
+          <t>661093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>431514</t>
+          <t>434844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518682</t>
+          <t>518991</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>171522</t>
+          <t>169521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227028</t>
+          <t>224726</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>626618</t>
+          <t>623774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>724512</t>
+          <t>726746</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1645636</t>
+          <t>1639712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1764278</t>
+          <t>1758301</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1640006</t>
+          <t>1642065</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1765241</t>
+          <t>1767566</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3314249</t>
+          <t>3317509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3482241</t>
+          <t>3499805</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1160247</t>
+          <t>1150562</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1268894</t>
+          <t>1266999</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1571495</t>
+          <t>1567944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1696208</t>
+          <t>1694246</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2758536</t>
+          <t>2739648</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2926477</t>
+          <t>2924048</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119023</t>
+          <t>118680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160216</t>
+          <t>161435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92744</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124523</t>
+          <t>124400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224040</t>
+          <t>221993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274882</t>
+          <t>275385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243117</t>
+          <t>240888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288681</t>
+          <t>285750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218803</t>
+          <t>219171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254287</t>
+          <t>253623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>471599</t>
+          <t>471121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530331</t>
+          <t>528116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82466</t>
+          <t>83808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122253</t>
+          <t>121634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88838</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>117970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>182715</t>
+          <t>182017</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229884</t>
+          <t>228027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>118767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160223</t>
+          <t>158815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>58282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83125</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184700</t>
+          <t>182576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236501</t>
+          <t>234593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185804</t>
+          <t>185392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229777</t>
+          <t>229523</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182208</t>
+          <t>180793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214824</t>
+          <t>215572</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378931</t>
+          <t>379739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>435992</t>
+          <t>434130</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88686</t>
+          <t>87506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124704</t>
+          <t>125376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99721</t>
+          <t>98362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130070</t>
+          <t>129671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193922</t>
+          <t>195612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244268</t>
+          <t>243661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183417</t>
+          <t>181533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>204353</t>
+          <t>203783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>271475</t>
+          <t>270106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>579454</t>
+          <t>570186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59423</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>80986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341135</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>688697</t>
+          <t>682828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>224354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80690</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88414</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299236</t>
+          <t>296693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215565</t>
+          <t>214770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280967</t>
+          <t>276162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195778</t>
+          <t>195539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>656975</t>
+          <t>606559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>439377</t>
+          <t>438824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1001554</t>
+          <t>1025912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5638,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425340</t>
+          <t>429741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>497025</t>
+          <t>502798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186538</t>
+          <t>214784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>466020</t>
+          <t>468622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>604335</t>
+          <t>578595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>936054</t>
+          <t>933449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>295360</t>
+          <t>293954</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>357991</t>
+          <t>364041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129849</t>
+          <t>144086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>328431</t>
+          <t>326561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405938</t>
+          <t>409550</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>657747</t>
+          <t>654322</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>88527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130998</t>
+          <t>130834</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92066</t>
+          <t>93783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148433</t>
+          <t>148836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189628</t>
+          <t>186426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266522</t>
+          <t>261998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186721</t>
+          <t>183927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232585</t>
+          <t>230733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>235457</t>
+          <t>242818</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>365641</t>
+          <t>367405</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>434566</t>
+          <t>428625</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>579437</t>
+          <t>579922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>139855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182029</t>
+          <t>181901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>338201</t>
+          <t>335392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>527031</t>
+          <t>504597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493362</t>
+          <t>492794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>683835</t>
+          <t>699992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66724</t>
+          <t>69279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117635</t>
+          <t>117664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>140453</t>
+          <t>138232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200173</t>
+          <t>199216</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88728</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138649</t>
+          <t>137095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296646</t>
+          <t>296530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>352204</t>
+          <t>346235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>402113</t>
+          <t>396450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>471373</t>
+          <t>474751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60593</t>
+          <t>59541</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>333827</t>
+          <t>335824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>386563</t>
+          <t>389008</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365403</t>
+          <t>365344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>430454</t>
+          <t>434458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>658355</t>
+          <t>656188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>921569</t>
+          <t>918430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>589941</t>
+          <t>587326</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1314345</t>
+          <t>1297691</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1400505</t>
+          <t>1390984</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2164218</t>
+          <t>2157715</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -7006,12 +7006,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1522156</t>
+          <t>1526883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2057404</t>
+          <t>1995162</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1199825</t>
+          <t>1221090</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1631043</t>
+          <t>1640859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2924556</t>
+          <t>2945128</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3644342</t>
+          <t>3642545</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>670539</t>
+          <t>688604</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>955264</t>
+          <t>956298</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1066464</t>
+          <t>1074768</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1436787</t>
+          <t>1427728</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1888902</t>
+          <t>1893672</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2352346</t>
+          <t>2325924</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IPAQ_MET-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73592</t>
+          <t>73108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95375</t>
+          <t>96941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199480</t>
+          <t>200832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243929</t>
+          <t>241781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>184973</t>
+          <t>184429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221087</t>
+          <t>220745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>394417</t>
+          <t>395539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>452483</t>
+          <t>451604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128285</t>
+          <t>132964</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>171334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104665</t>
+          <t>106027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141297</t>
+          <t>141476</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>246912</t>
+          <t>248905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>303419</t>
+          <t>304953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69778</t>
+          <t>67140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63634</t>
+          <t>61470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97565</t>
+          <t>96085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>193953</t>
+          <t>194125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233381</t>
+          <t>234600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>190332</t>
+          <t>189055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>227795</t>
+          <t>227878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>395068</t>
+          <t>392465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>451090</t>
+          <t>451117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91718</t>
+          <t>93641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128800</t>
+          <t>130177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119299</t>
+          <t>120834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156908</t>
+          <t>157863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221392</t>
+          <t>222100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274497</t>
+          <t>276544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80431</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>57913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230034</t>
+          <t>231023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276663</t>
+          <t>275778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101237</t>
+          <t>100930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>314156</t>
+          <t>318335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366892</t>
+          <t>371130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182599</t>
+          <t>183670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227180</t>
+          <t>227728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55113</t>
+          <t>56834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80891</t>
+          <t>82875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248191</t>
+          <t>245879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299076</t>
+          <t>298157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116866</t>
+          <t>117082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162531</t>
+          <t>163763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45363</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>74389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172413</t>
+          <t>173344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228809</t>
+          <t>227250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543029</t>
+          <t>542697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614764</t>
+          <t>611805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363125</t>
+          <t>361542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420318</t>
+          <t>419880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>918843</t>
+          <t>923487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1016407</t>
+          <t>1014276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>400739</t>
+          <t>400767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>469462</t>
+          <t>466338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347034</t>
+          <t>347568</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>405457</t>
+          <t>405801</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>762466</t>
+          <t>763128</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>853111</t>
+          <t>851122</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69262</t>
+          <t>69465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103397</t>
+          <t>104067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109615</t>
+          <t>106704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151593</t>
+          <t>152132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>262399</t>
+          <t>260109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>311721</t>
+          <t>309361</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>301926</t>
+          <t>302378</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>355625</t>
+          <t>356353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>578103</t>
+          <t>575637</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>653763</t>
+          <t>649844</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226122</t>
+          <t>227606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276523</t>
+          <t>275869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>339906</t>
+          <t>340220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>393741</t>
+          <t>395630</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>578049</t>
+          <t>579807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>653792</t>
+          <t>655430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92070</t>
+          <t>91846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54447</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96658</t>
+          <t>95715</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137276</t>
+          <t>137432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130869</t>
+          <t>131435</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167482</t>
+          <t>166081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>450612</t>
+          <t>446076</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>516655</t>
+          <t>514880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592451</t>
+          <t>593459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>666013</t>
+          <t>669600</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49362</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77269</t>
+          <t>78823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>527249</t>
+          <t>526526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596748</t>
+          <t>596314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>586479</t>
+          <t>582953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>661093</t>
+          <t>662598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>434844</t>
+          <t>435740</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518991</t>
+          <t>518505</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169521</t>
+          <t>171419</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224726</t>
+          <t>223747</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>623774</t>
+          <t>624468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>726746</t>
+          <t>725634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1639712</t>
+          <t>1636392</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1758301</t>
+          <t>1756987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1642065</t>
+          <t>1642085</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1767566</t>
+          <t>1763504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3317509</t>
+          <t>3312489</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3499805</t>
+          <t>3484734</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1150562</t>
+          <t>1155121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1266999</t>
+          <t>1263102</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1567944</t>
+          <t>1569014</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1694246</t>
+          <t>1694049</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2739648</t>
+          <t>2761453</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2924048</t>
+          <t>2927295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -4152,32 +4152,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>138604</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118680</t>
+          <t>133449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161435</t>
+          <t>178202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4187,32 +4187,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>108219</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92665</t>
+          <t>102884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124400</t>
+          <t>137947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4222,27 +4222,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>246823</t>
+          <t>272786</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221993</t>
+          <t>243231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275385</t>
+          <t>300337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4265,32 +4265,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264800</t>
+          <t>287009</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240888</t>
+          <t>261168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285750</t>
+          <t>310077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4300,32 +4300,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236922</t>
+          <t>258991</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219171</t>
+          <t>238845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253623</t>
+          <t>276906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4335,32 +4335,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>501722</t>
+          <t>546000</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>471121</t>
+          <t>515179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528116</t>
+          <t>579428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -4378,32 +4378,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101808</t>
+          <t>109042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83808</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121634</t>
+          <t>130354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4413,32 +4413,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102327</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>96262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117970</t>
+          <t>128829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>204134</t>
+          <t>220243</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>182017</t>
+          <t>195556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>228027</t>
+          <t>249174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -4491,17 +4491,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4526,17 +4526,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4608,32 +4608,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>138975</t>
+          <t>147506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118767</t>
+          <t>127233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158815</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4643,32 +4643,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71136</t>
+          <t>77604</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58282</t>
+          <t>64495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>93042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4678,32 +4678,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>210111</t>
+          <t>225110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182576</t>
+          <t>201729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234593</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -4721,32 +4721,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>207608</t>
+          <t>221487</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185392</t>
+          <t>199516</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229523</t>
+          <t>245120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4756,32 +4756,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>198205</t>
+          <t>219091</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180793</t>
+          <t>199734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215572</t>
+          <t>236878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>405813</t>
+          <t>440578</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>379739</t>
+          <t>410973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>434130</t>
+          <t>469350</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -4834,32 +4834,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>105630</t>
+          <t>114219</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87506</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125376</t>
+          <t>133476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4869,32 +4869,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113239</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98362</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129671</t>
+          <t>144556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4904,32 +4904,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>218870</t>
+          <t>240667</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195612</t>
+          <t>214798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243661</t>
+          <t>269141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4982,17 +4982,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5017,17 +5017,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5064,32 +5064,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110843</t>
+          <t>130470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>112505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>181533</t>
+          <t>150760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5099,32 +5099,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5134,32 +5134,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>138020</t>
+          <t>158895</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>138715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203783</t>
+          <t>183369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -5177,32 +5177,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>422280</t>
+          <t>195720</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>270106</t>
+          <t>173131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>570186</t>
+          <t>217270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5212,32 +5212,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>80619</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59735</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80986</t>
+          <t>92923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5247,32 +5247,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>492406</t>
+          <t>276339</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>253111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>682828</t>
+          <t>301806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -5290,32 +5290,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>145422</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54239</t>
+          <t>124819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224354</t>
+          <t>164630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5325,32 +5325,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>78453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59802</t>
+          <t>66953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80026</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5360,32 +5360,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>204749</t>
+          <t>223875</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84957</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296693</t>
+          <t>249144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -5403,17 +5403,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5520,32 +5520,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>244948</t>
+          <t>269230</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214770</t>
+          <t>239365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>276162</t>
+          <t>302845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5555,32 +5555,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>365839</t>
+          <t>181957</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195539</t>
+          <t>161132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>606559</t>
+          <t>203941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5590,32 +5590,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>610787</t>
+          <t>451186</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438824</t>
+          <t>414164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1025912</t>
+          <t>489476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -5633,32 +5633,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>462960</t>
+          <t>513471</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429741</t>
+          <t>476004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502798</t>
+          <t>550849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5668,32 +5668,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>361776</t>
+          <t>402766</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214784</t>
+          <t>377035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>468622</t>
+          <t>426908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>824736</t>
+          <t>916236</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578595</t>
+          <t>873682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>933449</t>
+          <t>962810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -5746,32 +5746,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>326911</t>
+          <t>349143</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>293954</t>
+          <t>318005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>364041</t>
+          <t>382422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250479</t>
+          <t>276489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144086</t>
+          <t>254841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326561</t>
+          <t>302132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>577390</t>
+          <t>625631</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>409550</t>
+          <t>588749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>654322</t>
+          <t>671954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5976,32 +5976,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>106839</t>
+          <t>124795</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88527</t>
+          <t>104953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130834</t>
+          <t>152049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6011,32 +6011,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>141917</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93783</t>
+          <t>123018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148836</t>
+          <t>160849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6046,32 +6046,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>232008</t>
+          <t>266712</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186426</t>
+          <t>239368</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261998</t>
+          <t>299735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -6089,32 +6089,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>208494</t>
+          <t>246727</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>183927</t>
+          <t>218762</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>230733</t>
+          <t>271312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6124,32 +6124,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>321722</t>
+          <t>363642</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>242818</t>
+          <t>339649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>367405</t>
+          <t>388333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6159,32 +6159,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>530216</t>
+          <t>610369</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>428625</t>
+          <t>577405</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>579922</t>
+          <t>645747</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -6202,32 +6202,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139855</t>
+          <t>170642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181901</t>
+          <t>222690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6237,32 +6237,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>394444</t>
+          <t>325291</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>335392</t>
+          <t>303020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>504597</t>
+          <t>349010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6272,32 +6272,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>554157</t>
+          <t>521733</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492794</t>
+          <t>491730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>699992</t>
+          <t>556418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -6315,17 +6315,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,17 +6350,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6432,32 +6432,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>91525</t>
+          <t>95437</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>74816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117664</t>
+          <t>121570</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6467,32 +6467,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76340</t>
+          <t>83691</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61760</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94584</t>
+          <t>102762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6502,32 +6502,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>179127</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>138232</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199216</t>
+          <t>211054</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -6545,32 +6545,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>113489</t>
+          <t>108525</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>85829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137095</t>
+          <t>131392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6580,32 +6580,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>323420</t>
+          <t>357475</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296530</t>
+          <t>327935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>346235</t>
+          <t>384936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6615,32 +6615,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>436909</t>
+          <t>466000</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>396450</t>
+          <t>427709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>474751</t>
+          <t>504793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -6658,32 +6658,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>35492</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59541</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6693,32 +6693,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>361611</t>
+          <t>403115</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>335824</t>
+          <t>374851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389008</t>
+          <t>431502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6728,32 +6728,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>397103</t>
+          <t>436382</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365344</t>
+          <t>399589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>434458</t>
+          <t>471399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -6771,17 +6771,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6841,17 +6841,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6888,32 +6888,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>831734</t>
+          <t>922004</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>656188</t>
+          <t>864269</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>918430</t>
+          <t>980405</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6923,32 +6923,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>773880</t>
+          <t>631812</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>587326</t>
+          <t>592785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1297691</t>
+          <t>670898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6958,32 +6958,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1605614</t>
+          <t>1553816</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1390984</t>
+          <t>1477433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2157715</t>
+          <t>1626174</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -7001,32 +7001,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1679632</t>
+          <t>1572938</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1526883</t>
+          <t>1504142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1995162</t>
+          <t>1632051</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7036,32 +7036,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1512169</t>
+          <t>1682585</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1221090</t>
+          <t>1632155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1640859</t>
+          <t>1736024</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7071,32 +7071,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3191801</t>
+          <t>3255523</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2945128</t>
+          <t>3176997</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3642545</t>
+          <t>3348410</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -7114,32 +7114,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>864694</t>
+          <t>947534</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>688604</t>
+          <t>894073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>956298</t>
+          <t>1000283</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7149,32 +7149,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1291709</t>
+          <t>1320997</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1074768</t>
+          <t>1269554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1427728</t>
+          <t>1369896</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7184,32 +7184,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2156403</t>
+          <t>2268531</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1893672</t>
+          <t>2186422</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2325924</t>
+          <t>2343627</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -7227,17 +7227,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7262,17 +7262,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7297,17 +7297,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
